--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,501 +443,421 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03787469866477696</v>
+        <v>0.01432884651656638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.514237971154292</v>
+        <v>-0.09044786781418415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2300475290828927</v>
+        <v>-0.09571677207350347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0799403904872631</v>
+        <v>0.02604304002779332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.10976596319377</v>
+        <v>0.1112539613917412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2275817825526433</v>
+        <v>-0.09935246966918143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09187938525916992</v>
+        <v>0.03695191295219685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1909423556523765</v>
+        <v>-0.1309754822014174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04381649834298566</v>
+        <v>-0.0508225159390901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.04129263708559629</v>
+        <v>-0.08723719567653064</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1911067661991056</v>
+        <v>-0.02112512338014438</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.003390424554334842</v>
+        <v>-0.5421754827995869</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.09773758725346664</v>
+        <v>0.05929281954438022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1192212906683472</v>
+        <v>-0.1286488041738784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1431851366949871</v>
+        <v>-0.07113649791560252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0822932177080352</v>
+        <v>0.1248391129977296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.01364811818314811</v>
+        <v>0.08934551424749233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02177711158527978</v>
+        <v>-0.1463476300554827</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005311805931040476</v>
+        <v>0.08979038558042897</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0979119559101666</v>
+        <v>-0.04619918859336983</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07799551423518164</v>
+        <v>0.07008594623279328</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01526734732365108</v>
+        <v>0.07514577129280858</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.08254989852858637</v>
+        <v>-0.1443854281375146</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2043458156341375</v>
+        <v>0.03251065491741757</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2428065890784031</v>
+        <v>-0.0204606789910805</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02190562191654158</v>
+        <v>0.04674120346448168</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06577187923953851</v>
+        <v>-0.03193421208933655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06476218112345948</v>
+        <v>0.1276098355990334</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.004670034056878236</v>
+        <v>-0.03100011978830897</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02511158258033529</v>
+        <v>-0.01678420405121739</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.07489610045507178</v>
+        <v>0.06771486265996944</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1376082911985373</v>
+        <v>0.0856322930575214</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1401637680812392</v>
+        <v>0.08467941952157858</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.1400307347386435</v>
+        <v>-0.09070877611445745</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.08496709080689516</v>
+        <v>0.1125279080141107</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0725480103105459</v>
+        <v>-0.09705832332627697</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2208022694113484</v>
+        <v>0.03441294609064503</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.110057370765295</v>
+        <v>-0.03157328010638807</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.05949992661029433</v>
+        <v>-0.01386363720552993</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1770026302265114</v>
+        <v>0.003307051407730083</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.2816481399783905</v>
+        <v>-0.01989535072365249</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2005807657230637</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>-0.09552996019279963</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.1749634582819543</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.1244893237250476</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.1702999188737616</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.1132537515075282</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>-0.04429706809083304</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>-0.08979762871876887</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>-0.05664682470367508</v>
+        <v>-0.03059271399744669</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,417 +447,587 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01432884651656638</v>
+        <v>0.05325144750772384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09044786781418415</v>
+        <v>0.001050072570247629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09571677207350347</v>
+        <v>-0.1174828653845468</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02604304002779332</v>
+        <v>0.1653663211450149</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1112539613917412</v>
+        <v>0.3911900638671512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.09935246966918143</v>
+        <v>0.18997138435816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03695191295219685</v>
+        <v>0.2895627570186876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1309754822014174</v>
+        <v>0.001069623505445052</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0508225159390901</v>
+        <v>-0.09808108848960256</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08723719567653064</v>
+        <v>-0.005151883726822952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.02112512338014438</v>
+        <v>0.250079687399733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5421754827995869</v>
+        <v>-0.1440797932314283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05929281954438022</v>
+        <v>-0.4038622820417867</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1286488041738784</v>
+        <v>-0.01586163246236341</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07113649791560252</v>
+        <v>-0.1076149861084598</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1248391129977296</v>
+        <v>0.2777002177893351</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.08934551424749233</v>
+        <v>0.1533854528981161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1463476300554827</v>
+        <v>0.31239430495456</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08979038558042897</v>
+        <v>0.1401242857492412</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.04619918859336983</v>
+        <v>0.03910708742211549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07008594623279328</v>
+        <v>-0.1992853247107661</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07514577129280858</v>
+        <v>0.2255925296813722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1443854281375146</v>
+        <v>0.211640957085053</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03251065491741757</v>
+        <v>0.09797970458311805</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0204606789910805</v>
+        <v>0.2260495342296122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04674120346448168</v>
+        <v>0.1857681186365856</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.03193421208933655</v>
+        <v>0.02584532746390284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1276098355990334</v>
+        <v>0.211903115834279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.03100011978830897</v>
+        <v>0.2374084293086753</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01678420405121739</v>
+        <v>0.2107311839161445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.06771486265996944</v>
+        <v>0.03001736483066483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0856322930575214</v>
+        <v>0.06738276955536358</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.08467941952157858</v>
+        <v>0.09361560977745206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.09070877611445745</v>
+        <v>-0.07442577719661521</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1125279080141107</v>
+        <v>-0.165397955721645</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.09705832332627697</v>
+        <v>0.1776145296455185</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.03441294609064503</v>
+        <v>0.2091486836005251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.03157328010638807</v>
+        <v>-0.01877492978899059</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.01386363720552993</v>
+        <v>0.03533945385616203</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.003307051407730083</v>
+        <v>0.09338790531852956</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.01989535072365249</v>
+        <v>0.0598917491451138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.06092695035238299</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.08794571128213464</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.09167763408884107</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.1853228633524058</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.01446883383249281</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>-0.08568925423259485</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.1307242339198468</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.04503407642104158</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>-0.1965417110123699</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.1725341536131873</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.0001784327218528991</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1779325867873137</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3644045482723983</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2144328761141746</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.06475925862831418</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1885916401667298</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>-0.03059271399744669</v>
+      <c r="B59" t="n">
+        <v>0.1955122622928803</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>-0.2263663502912818</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05325144750772384</v>
+        <v>-0.03759272777162127</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001050072570247629</v>
+        <v>-0.04903698204543939</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1174828653845468</v>
+        <v>0.06807185625640597</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1653663211450149</v>
+        <v>0.1271939256148046</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3911900638671512</v>
+        <v>0.4365669571525839</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.18997138435816</v>
+        <v>-0.1604629563713845</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2895627570186876</v>
+        <v>0.3467242645579275</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001069623505445052</v>
+        <v>-0.02509938136063733</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.09808108848960256</v>
+        <v>0.1196605422060365</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.005151883726822952</v>
+        <v>-0.07768455220415964</v>
       </c>
     </row>
     <row r="12">
@@ -547,487 +547,417 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.250079687399733</v>
+        <v>0.2044525489136211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1440797932314283</v>
+        <v>-0.4468398306868873</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4038622820417867</v>
+        <v>0.0007876489036734493</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.01586163246236341</v>
+        <v>-0.06726548754386566</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1076149861084598</v>
+        <v>0.4100384971551144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2777002177893351</v>
+        <v>0.08135272685133024</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1533854528981161</v>
+        <v>0.4027421985527894</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.31239430495456</v>
+        <v>0.03131706079959897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1401242857492412</v>
+        <v>-0.0693566905286315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.03910708742211549</v>
+        <v>-0.146223876575236</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1992853247107661</v>
+        <v>0.1719560739464677</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2255925296813722</v>
+        <v>0.1740703849726498</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.211640957085053</v>
+        <v>0.1075383785446095</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.09797970458311805</v>
+        <v>0.2139329228001569</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2260495342296122</v>
+        <v>0.201939637665186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1857681186365856</v>
+        <v>0.06549199789954302</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02584532746390284</v>
+        <v>0.1210179674985288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.211903115834279</v>
+        <v>0.1603278566761208</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2374084293086753</v>
+        <v>0.1507170610190425</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2107311839161445</v>
+        <v>0.002712426627021881</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.03001736483066483</v>
+        <v>-0.1896351792653971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.06738276955536358</v>
+        <v>-0.06878630135228328</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.09361560977745206</v>
+        <v>0.09037075970851766</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.07442577719661521</v>
+        <v>0.1515710447264544</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.165397955721645</v>
+        <v>0.02864096169237385</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1776145296455185</v>
+        <v>-0.05318442911797063</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2091486836005251</v>
+        <v>0.09126381609925781</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01877492978899059</v>
+        <v>0.04923040911177735</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.03533945385616203</v>
+        <v>0.02393288808161226</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.09338790531852956</v>
+        <v>0.1349537716662137</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0598917491451138</v>
+        <v>0.02186422820428241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.06092695035238299</v>
+        <v>-0.08799297153704887</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.08794571128213464</v>
+        <v>-0.07846568910231014</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.09167763408884107</v>
+        <v>-0.04756142583740049</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1853228633524058</v>
+        <v>-0.0625948242502633</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.01446883383249281</v>
+        <v>0.02918107605432703</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.08568925423259485</v>
+        <v>0.00278832503609033</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1307242339198468</v>
+        <v>0.1292417111809274</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.04503407642104158</v>
+        <v>-0.4042113006899367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1965417110123699</v>
+        <v>0.1936685576168969</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1725341536131873</v>
+        <v>-0.05444503521438594</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0001784327218528991</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.1779325867873137</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-0.3644045482723983</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.2144328761141746</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>-0.06475925862831418</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.1885916401667298</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.1955122622928803</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>-0.2263663502912818</v>
+        <v>-0.302509803963821</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/env_silhouettes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.03759272777162127</v>
+        <v>0.05325144750772384</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04903698204543939</v>
+        <v>0.001050072570247629</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06807185625640597</v>
+        <v>-0.1174828653845468</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1271939256148046</v>
+        <v>0.1653663211450149</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4365669571525839</v>
+        <v>0.3911900638671512</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1604629563713845</v>
+        <v>0.18997138435816</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3467242645579275</v>
+        <v>0.2895627570186876</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02509938136063733</v>
+        <v>0.001069623505445052</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1196605422060365</v>
+        <v>-0.09808108848960256</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.07768455220415964</v>
+        <v>-0.005151883726822952</v>
       </c>
     </row>
     <row r="12">
@@ -547,417 +547,487 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2044525489136211</v>
+        <v>0.250079687399733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4468398306868873</v>
+        <v>-0.1440797932314283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0007876489036734493</v>
+        <v>-0.4038622820417867</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.06726548754386566</v>
+        <v>-0.01586163246236341</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4100384971551144</v>
+        <v>-0.1076149861084598</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08135272685133024</v>
+        <v>0.2777002177893351</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4027421985527894</v>
+        <v>0.1533854528981161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03131706079959897</v>
+        <v>0.31239430495456</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0693566905286315</v>
+        <v>0.1401242857492412</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.146223876575236</v>
+        <v>0.03910708742211549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1719560739464677</v>
+        <v>-0.1992853247107661</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1740703849726498</v>
+        <v>0.2255925296813722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1075383785446095</v>
+        <v>0.211640957085053</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2139329228001569</v>
+        <v>0.09797970458311805</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.201939637665186</v>
+        <v>0.2260495342296122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06549199789954302</v>
+        <v>0.1857681186365856</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1210179674985288</v>
+        <v>0.02584532746390284</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1603278566761208</v>
+        <v>0.211903115834279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1507170610190425</v>
+        <v>0.2374084293086753</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002712426627021881</v>
+        <v>0.2107311839161445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1896351792653971</v>
+        <v>0.03001736483066483</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.06878630135228328</v>
+        <v>0.06738276955536358</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.09037075970851766</v>
+        <v>0.09361560977745206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1515710447264544</v>
+        <v>-0.07442577719661521</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.02864096169237385</v>
+        <v>-0.165397955721645</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.05318442911797063</v>
+        <v>0.1776145296455185</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.09126381609925781</v>
+        <v>0.2091486836005251</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.04923040911177735</v>
+        <v>-0.01877492978899059</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.02393288808161226</v>
+        <v>0.03533945385616203</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1349537716662137</v>
+        <v>0.09338790531852956</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.02186422820428241</v>
+        <v>0.0598917491451138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.08799297153704887</v>
+        <v>-0.06092695035238299</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.07846568910231014</v>
+        <v>0.08794571128213464</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.04756142583740049</v>
+        <v>0.09167763408884107</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0625948242502633</v>
+        <v>0.1853228633524058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.02918107605432703</v>
+        <v>0.01446883383249281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.00278832503609033</v>
+        <v>-0.08568925423259485</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1292417111809274</v>
+        <v>0.1307242339198468</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.4042113006899367</v>
+        <v>0.04503407642104158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1936685576168969</v>
+        <v>-0.1965417110123699</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.05444503521438594</v>
+        <v>-0.1725341536131873</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.0001784327218528991</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1779325867873137</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-0.3644045482723983</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2144328761141746</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>-0.06475925862831418</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1885916401667298</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.1955122622928803</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>-0.302509803963821</v>
+      <c r="B60" t="n">
+        <v>-0.2263663502912818</v>
       </c>
     </row>
   </sheetData>
